--- a/education_forms/019_hybrid_classroom_participation_behavior_survey--education_forms.xlsx
+++ b/education_forms/019_hybrid_classroom_participation_behavior_survey--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>survey</t>
+          <t>participation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Survey Questions</t>
+          <t>How do you usually participate in classes?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>survey</t>
+          <t>time_spent_in_class</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>survey</t>
+          <t>How many hours do you usually spend in a class?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>challenges</t>
+          <t>start_time</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>challenges</t>
+          <t>When do you usually start attending classes?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>preferred_time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>What is your preferred time to attend classes?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Email Address</t>
+          <t>How do you usually communicate with instructors or peers?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>challenges</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phone Number</t>
+          <t>What are some common challenges you face while participating in classes?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Timestamp</t>
+          <t>What is your email address?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>What is your phone number?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,366 +722,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Do you have any comments about the class?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Timestamp</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>survey</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>survey</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>survey</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>survey</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>challenges</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>challenges</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>feedback</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Feedback</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Email Address</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Phone Number</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Timestamp</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Timestamp</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>survey</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>survey</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>survey</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>survey</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,170 +781,170 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>survey_choices</t>
+          <t>participation_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>survey_choices</t>
+          <t>participation_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>survey_choices</t>
+          <t>participation_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>survey_choices</t>
+          <t>participation_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'option_4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Option 4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>survey_choices</t>
+          <t>participation_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'option_5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Option 5'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>survey_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>survey_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>survey_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>survey_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'option_4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Option 4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>survey_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'option_5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Option 5'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1301,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1318,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1335,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'option_4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Option 4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1369,437 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'option_5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Option 5'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>survey_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'value':_'option_1'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>survey_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'value':_'option_2'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>survey_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'value':_'option_3'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>survey_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'value':_'option_4'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 4'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>survey_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'value':_'option_5'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 5'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>survey_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'value':_'option_1'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>survey_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'value':_'option_2'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>survey_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'value':_'option_3'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>survey_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'value':_'option_4'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 4'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>survey_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'value':_'option_5'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 5'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>challenges_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'value':_'option_1'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>challenges_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'value':_'option_2'}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>challenges_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'value':_'option_3'}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>challenges_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'value':_'option_4'}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 4'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>challenges_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>{'value':_'option_5'}</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 5'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>survey_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>{'value':_'option_1'}</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>survey_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'value':_'option_2'}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>survey_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'value':_'option_3'}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>survey_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'value':_'option_4'}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 4'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>survey_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'value':_'option_5'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 5'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>survey_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'value':_'option_1'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>survey_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'value':_'option_2'}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>survey_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'value':_'option_3'}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>survey_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'value':_'option_4'}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 4'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>survey_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'value':_'option_5'}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 5'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
